--- a/results/comparison_vs_nayma/comparison_table.xlsx
+++ b/results/comparison_vs_nayma/comparison_table.xlsx
@@ -525,52 +525,52 @@
         <v>0.945782</v>
       </c>
       <c r="D2">
-        <v>0.965318</v>
+        <v>0.953757</v>
       </c>
       <c r="E2">
-        <v>0.917542</v>
+        <v>0.857976</v>
       </c>
       <c r="F2">
-        <v>0.965318</v>
+        <v>0.9662809999999999</v>
       </c>
       <c r="G2">
-        <v>0.912562</v>
+        <v>0.892709</v>
       </c>
       <c r="H2">
-        <v>0.954721</v>
+        <v>0.963391</v>
       </c>
       <c r="I2">
-        <v>0.905653</v>
+        <v>0.880686</v>
       </c>
       <c r="J2">
-        <v>0.972062</v>
+        <v>0.952794</v>
       </c>
       <c r="K2">
-        <v>0.938025</v>
+        <v>0.860743</v>
       </c>
       <c r="L2">
-        <v>0.959538</v>
+        <v>0.964355</v>
       </c>
       <c r="M2">
-        <v>0.903589</v>
+        <v>0.885124</v>
       </c>
       <c r="N2">
-        <v>0.953757</v>
+        <v>0.961464</v>
       </c>
       <c r="O2">
-        <v>0.882076</v>
+        <v>0.884652</v>
       </c>
       <c r="P2">
-        <v>0.964355</v>
+        <v>0.947013</v>
       </c>
       <c r="Q2">
-        <v>0.907594</v>
+        <v>0.840493</v>
       </c>
       <c r="R2">
-        <v>0.958574</v>
+        <v>0.957611</v>
       </c>
       <c r="S2">
-        <v>0.898133</v>
+        <v>0.864536</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -584,52 +584,52 @@
         <v>0.954981</v>
       </c>
       <c r="D3">
-        <v>0.8777779999999999</v>
+        <v>0.922222</v>
       </c>
       <c r="E3">
-        <v>0.876413</v>
+        <v>0.922139</v>
       </c>
       <c r="F3">
+        <v>0.855556</v>
+      </c>
+      <c r="G3">
+        <v>0.854135</v>
+      </c>
+      <c r="H3">
         <v>0.922222</v>
       </c>
-      <c r="G3">
+      <c r="I3">
         <v>0.922139</v>
       </c>
-      <c r="H3">
-        <v>0.9</v>
-      </c>
-      <c r="I3">
-        <v>0.898457</v>
-      </c>
       <c r="J3">
-        <v>0.888889</v>
+        <v>0.911111</v>
       </c>
       <c r="K3">
-        <v>0.888889</v>
+        <v>0.910944</v>
       </c>
       <c r="L3">
+        <v>0.866667</v>
+      </c>
+      <c r="M3">
+        <v>0.8665</v>
+      </c>
+      <c r="N3">
+        <v>0.922222</v>
+      </c>
+      <c r="O3">
+        <v>0.922139</v>
+      </c>
+      <c r="P3">
         <v>0.933333</v>
       </c>
-      <c r="M3">
+      <c r="Q3">
         <v>0.933333</v>
       </c>
-      <c r="N3">
-        <v>0.8777779999999999</v>
-      </c>
-      <c r="O3">
-        <v>0.877694</v>
-      </c>
-      <c r="P3">
-        <v>0.911111</v>
-      </c>
-      <c r="Q3">
-        <v>0.910944</v>
-      </c>
       <c r="R3">
-        <v>0.8777779999999999</v>
+        <v>0.844444</v>
       </c>
       <c r="S3">
-        <v>0.877694</v>
+        <v>0.843032</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -643,52 +643,52 @@
         <v>0.965253</v>
       </c>
       <c r="D4">
-        <v>0.911833</v>
+        <v>0.907917</v>
       </c>
       <c r="E4">
-        <v>0.9117150000000001</v>
+        <v>0.907524</v>
       </c>
       <c r="F4">
-        <v>0.914667</v>
+        <v>0.911</v>
       </c>
       <c r="G4">
-        <v>0.914624</v>
+        <v>0.910577</v>
       </c>
       <c r="H4">
-        <v>0.914333</v>
+        <v>0.910833</v>
       </c>
       <c r="I4">
-        <v>0.914345</v>
+        <v>0.910425</v>
       </c>
       <c r="J4">
-        <v>0.918083</v>
+        <v>0.91275</v>
       </c>
       <c r="K4">
-        <v>0.918014</v>
+        <v>0.91237</v>
       </c>
       <c r="L4">
-        <v>0.909833</v>
+        <v>0.913083</v>
       </c>
       <c r="M4">
-        <v>0.909905</v>
+        <v>0.912723</v>
       </c>
       <c r="N4">
-        <v>0.911833</v>
+        <v>0.91325</v>
       </c>
       <c r="O4">
-        <v>0.911903</v>
+        <v>0.9130549999999999</v>
       </c>
       <c r="P4">
-        <v>0.91325</v>
+        <v>0.9097499999999999</v>
       </c>
       <c r="Q4">
-        <v>0.912936</v>
+        <v>0.909428</v>
       </c>
       <c r="R4">
-        <v>0.92025</v>
+        <v>0.910083</v>
       </c>
       <c r="S4">
-        <v>0.920233</v>
+        <v>0.9095259999999999</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -702,52 +702,52 @@
         <v>0.954848</v>
       </c>
       <c r="D5">
-        <v>0.977366</v>
+        <v>0.976595</v>
       </c>
       <c r="E5">
-        <v>0.95992</v>
+        <v>0.9515439999999999</v>
       </c>
       <c r="F5">
-        <v>0.975309</v>
+        <v>0.977623</v>
       </c>
       <c r="G5">
-        <v>0.951728</v>
+        <v>0.95474</v>
       </c>
       <c r="H5">
-        <v>0.976337</v>
+        <v>0.979295</v>
       </c>
       <c r="I5">
-        <v>0.953296</v>
+        <v>0.9577290000000001</v>
       </c>
       <c r="J5">
-        <v>0.971708</v>
+        <v>0.975952</v>
       </c>
       <c r="K5">
-        <v>0.942134</v>
+        <v>0.95196</v>
       </c>
       <c r="L5">
-        <v>0.976595</v>
+        <v>0.9772380000000001</v>
       </c>
       <c r="M5">
-        <v>0.956477</v>
+        <v>0.954467</v>
       </c>
       <c r="N5">
-        <v>0.975309</v>
+        <v>0.974666</v>
       </c>
       <c r="O5">
-        <v>0.9479340000000001</v>
+        <v>0.95265</v>
       </c>
       <c r="P5">
-        <v>0.977752</v>
+        <v>0.97518</v>
       </c>
       <c r="Q5">
-        <v>0.953707</v>
+        <v>0.949056</v>
       </c>
       <c r="R5">
         <v>0.97338</v>
       </c>
       <c r="S5">
-        <v>0.954712</v>
+        <v>0.936039</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -761,52 +761,52 @@
         <v>0.982218</v>
       </c>
       <c r="D6">
-        <v>0.962337</v>
+        <v>0.959964</v>
       </c>
       <c r="E6">
-        <v>0.962295</v>
+        <v>0.959686</v>
       </c>
       <c r="F6">
-        <v>0.964709</v>
+        <v>0.954033</v>
       </c>
       <c r="G6">
-        <v>0.964569</v>
+        <v>0.953811</v>
       </c>
       <c r="H6">
-        <v>0.9632270000000001</v>
+        <v>0.956109</v>
       </c>
       <c r="I6">
-        <v>0.963131</v>
+        <v>0.9558720000000001</v>
       </c>
       <c r="J6">
-        <v>0.967675</v>
+        <v>0.9567020000000001</v>
       </c>
       <c r="K6">
-        <v>0.967623</v>
+        <v>0.956427</v>
       </c>
       <c r="L6">
+        <v>0.960854</v>
+      </c>
+      <c r="M6">
+        <v>0.960224</v>
+      </c>
+      <c r="N6">
+        <v>0.957888</v>
+      </c>
+      <c r="O6">
+        <v>0.9574549999999999</v>
+      </c>
+      <c r="P6">
         <v>0.96204</v>
       </c>
-      <c r="M6">
-        <v>0.962032</v>
-      </c>
-      <c r="N6">
-        <v>0.96204</v>
-      </c>
-      <c r="O6">
-        <v>0.961923</v>
-      </c>
-      <c r="P6">
-        <v>0.964413</v>
-      </c>
       <c r="Q6">
-        <v>0.964306</v>
+        <v>0.961533</v>
       </c>
       <c r="R6">
-        <v>0.964413</v>
+        <v>0.956999</v>
       </c>
       <c r="S6">
-        <v>0.964436</v>
+        <v>0.956685</v>
       </c>
     </row>
     <row r="7" spans="1:19">
@@ -820,52 +820,52 @@
         <v>0.823483</v>
       </c>
       <c r="D7">
-        <v>0.785714</v>
+        <v>0.666667</v>
       </c>
       <c r="E7">
-        <v>0.779869</v>
+        <v>0.659693</v>
       </c>
       <c r="F7">
-        <v>0.730159</v>
+        <v>0.7380949999999999</v>
       </c>
       <c r="G7">
-        <v>0.722718</v>
+        <v>0.732086</v>
       </c>
       <c r="H7">
-        <v>0.777778</v>
+        <v>0.690476</v>
       </c>
       <c r="I7">
-        <v>0.771497</v>
+        <v>0.681628</v>
       </c>
       <c r="J7">
-        <v>0.801587</v>
+        <v>0.698413</v>
       </c>
       <c r="K7">
-        <v>0.795833</v>
+        <v>0.688932</v>
       </c>
       <c r="L7">
-        <v>0.753968</v>
+        <v>0.714286</v>
       </c>
       <c r="M7">
-        <v>0.74272</v>
+        <v>0.7052580000000001</v>
       </c>
       <c r="N7">
-        <v>0.722222</v>
+        <v>0.706349</v>
       </c>
       <c r="O7">
-        <v>0.716564</v>
+        <v>0.697545</v>
       </c>
       <c r="P7">
-        <v>0.7380949999999999</v>
+        <v>0.698413</v>
       </c>
       <c r="Q7">
-        <v>0.723211</v>
+        <v>0.6904130000000001</v>
       </c>
       <c r="R7">
-        <v>0.746032</v>
+        <v>0.714286</v>
       </c>
       <c r="S7">
-        <v>0.73011</v>
+        <v>0.706497</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -879,52 +879,52 @@
         <v>0.952755</v>
       </c>
       <c r="D8">
-        <v>0.92472</v>
+        <v>0.938111</v>
       </c>
       <c r="E8">
-        <v>0.920548</v>
+        <v>0.936048</v>
       </c>
       <c r="F8">
-        <v>0.923996</v>
+        <v>0.936301</v>
       </c>
       <c r="G8">
-        <v>0.919381</v>
+        <v>0.934096</v>
       </c>
       <c r="H8">
-        <v>0.918929</v>
+        <v>0.933768</v>
       </c>
       <c r="I8">
-        <v>0.914344</v>
+        <v>0.931558</v>
       </c>
       <c r="J8">
-        <v>0.923272</v>
+        <v>0.933406</v>
       </c>
       <c r="K8">
-        <v>0.91887</v>
+        <v>0.931027</v>
       </c>
       <c r="L8">
-        <v>0.923272</v>
+        <v>0.933044</v>
       </c>
       <c r="M8">
-        <v>0.9191009999999999</v>
+        <v>0.930688</v>
       </c>
       <c r="N8">
-        <v>0.92291</v>
+        <v>0.937025</v>
       </c>
       <c r="O8">
-        <v>0.918509</v>
+        <v>0.934841</v>
       </c>
       <c r="P8">
-        <v>0.922186</v>
+        <v>0.933406</v>
       </c>
       <c r="Q8">
-        <v>0.918008</v>
+        <v>0.930991</v>
       </c>
       <c r="R8">
-        <v>0.923272</v>
+        <v>0.93232</v>
       </c>
       <c r="S8">
-        <v>0.9188539999999999</v>
+        <v>0.929907</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -938,52 +938,52 @@
         <v>0.968468</v>
       </c>
       <c r="D9">
+        <v>0.819865</v>
+      </c>
+      <c r="E9">
+        <v>0.812794</v>
+      </c>
+      <c r="F9">
+        <v>0.799663</v>
+      </c>
+      <c r="G9">
+        <v>0.793069</v>
+      </c>
+      <c r="H9">
         <v>0.784512</v>
       </c>
-      <c r="E9">
-        <v>0.785361</v>
-      </c>
-      <c r="F9">
-        <v>0.786195</v>
-      </c>
-      <c r="G9">
-        <v>0.785436</v>
-      </c>
-      <c r="H9">
+      <c r="I9">
+        <v>0.777318</v>
+      </c>
+      <c r="J9">
+        <v>0.801347</v>
+      </c>
+      <c r="K9">
+        <v>0.796065</v>
+      </c>
+      <c r="L9">
+        <v>0.806397</v>
+      </c>
+      <c r="M9">
+        <v>0.799725</v>
+      </c>
+      <c r="N9">
+        <v>0.777778</v>
+      </c>
+      <c r="O9">
+        <v>0.7663450000000001</v>
+      </c>
+      <c r="P9">
+        <v>0.824916</v>
+      </c>
+      <c r="Q9">
+        <v>0.8200190000000001</v>
+      </c>
+      <c r="R9">
         <v>0.782828</v>
       </c>
-      <c r="I9">
-        <v>0.782417</v>
-      </c>
-      <c r="J9">
-        <v>0.777778</v>
-      </c>
-      <c r="K9">
-        <v>0.7774489999999999</v>
-      </c>
-      <c r="L9">
-        <v>0.755892</v>
-      </c>
-      <c r="M9">
-        <v>0.756829</v>
-      </c>
-      <c r="N9">
-        <v>0.750842</v>
-      </c>
-      <c r="O9">
-        <v>0.752431</v>
-      </c>
-      <c r="P9">
-        <v>0.737374</v>
-      </c>
-      <c r="Q9">
-        <v>0.73961</v>
-      </c>
-      <c r="R9">
-        <v>0.779461</v>
-      </c>
       <c r="S9">
-        <v>0.781327</v>
+        <v>0.775441</v>
       </c>
     </row>
   </sheetData>
